--- a/xls/square_eigen_20_quad4_10_un.xlsx
+++ b/xls/square_eigen_20_quad4_10_un.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
   <si>
     <t>type w</t>
   </si>
@@ -72,148 +72,136 @@
     <t>PiecewisePolynomial{:Linear2D}</t>
   </si>
   <si>
-    <t>1.451759189042607</t>
-  </si>
-  <si>
-    <t>4.820931949236769e-5</t>
-  </si>
-  <si>
-    <t>2.9354218414564874</t>
-  </si>
-  <si>
-    <t>4.868167546490896e-5</t>
-  </si>
-  <si>
-    <t>2.6475960801937646</t>
-  </si>
-  <si>
-    <t>4.736100840077414e-5</t>
-  </si>
-  <si>
-    <t>5.375336439797121</t>
-  </si>
-  <si>
-    <t>4.714725478881707e-5</t>
-  </si>
-  <si>
-    <t>6.303248671888927</t>
-  </si>
-  <si>
-    <t>27.83313826572502</t>
-  </si>
-  <si>
-    <t>7.384321624921167</t>
-  </si>
-  <si>
-    <t>19.07374826419032</t>
-  </si>
-  <si>
-    <t>7.980681305744186</t>
-  </si>
-  <si>
-    <t>6.828019694178725</t>
-  </si>
-  <si>
-    <t>7.839113351082228</t>
-  </si>
-  <si>
-    <t>3.3017516134316325</t>
-  </si>
-  <si>
-    <t>8.310265755565059</t>
-  </si>
-  <si>
-    <t>1.3262376319476146</t>
-  </si>
-  <si>
-    <t>7.6961530473198625</t>
-  </si>
-  <si>
-    <t>1.083928398878812</t>
-  </si>
-  <si>
-    <t>8.014366223454473</t>
-  </si>
-  <si>
-    <t>14.027398770448878</t>
-  </si>
-  <si>
-    <t>8.245923729174574</t>
-  </si>
-  <si>
-    <t>0.006136037679775494</t>
-  </si>
-  <si>
-    <t>8.959836059235588</t>
-  </si>
-  <si>
-    <t>0.13431725348115703</t>
-  </si>
-  <si>
-    <t>8.466633365525551</t>
-  </si>
-  <si>
-    <t>0.1860234512243256</t>
-  </si>
-  <si>
-    <t>8.698306119743329</t>
-  </si>
-  <si>
-    <t>0.1870434932464765</t>
-  </si>
-  <si>
-    <t>9.107806587099345</t>
-  </si>
-  <si>
-    <t>0.29379499326139547</t>
-  </si>
-  <si>
-    <t>8.464932956537371</t>
-  </si>
-  <si>
-    <t>0.28988991292065214</t>
-  </si>
-  <si>
-    <t>9.100379450941402</t>
-  </si>
-  <si>
-    <t>0.32025495920552016</t>
-  </si>
-  <si>
-    <t>8.768049328626203</t>
-  </si>
-  <si>
-    <t>0.3307193647355082</t>
-  </si>
-  <si>
-    <t>8.879921340324522</t>
-  </si>
-  <si>
-    <t>0.33932514209553827</t>
-  </si>
-  <si>
-    <t>8.664677454589723</t>
-  </si>
-  <si>
-    <t>0.37692503324441773</t>
-  </si>
-  <si>
-    <t>8.639716365671148</t>
-  </si>
-  <si>
-    <t>0.2801778811767701</t>
-  </si>
-  <si>
-    <t>8.996166624733206</t>
-  </si>
-  <si>
-    <t>0.22886301549965124</t>
-  </si>
-  <si>
-    <t>8.72225422918908</t>
-  </si>
-  <si>
-    <t>0.23515293332154263</t>
+    <t>1.495049543670467</t>
+  </si>
+  <si>
+    <t>4.7303599876871854e-5</t>
+  </si>
+  <si>
+    <t>2.643913295679708</t>
+  </si>
+  <si>
+    <t>5.319907279619617e-5</t>
+  </si>
+  <si>
+    <t>4.580370067462417</t>
+  </si>
+  <si>
+    <t>50.241034499459644</t>
+  </si>
+  <si>
+    <t>5.057311728009055</t>
+  </si>
+  <si>
+    <t>50.18890978972512</t>
+  </si>
+  <si>
+    <t>5.2054734050921345</t>
+  </si>
+  <si>
+    <t>22.826141080233448</t>
+  </si>
+  <si>
+    <t>6.573196868088008</t>
+  </si>
+  <si>
+    <t>29.570007489956694</t>
+  </si>
+  <si>
+    <t>7.026136281891266</t>
+  </si>
+  <si>
+    <t>27.2812137706246</t>
+  </si>
+  <si>
+    <t>5.5425051000338</t>
+  </si>
+  <si>
+    <t>19.034822940573875</t>
+  </si>
+  <si>
+    <t>7.998828351942611</t>
+  </si>
+  <si>
+    <t>8.241194703696582</t>
+  </si>
+  <si>
+    <t>8.770708392054617</t>
+  </si>
+  <si>
+    <t>6.374186087582522</t>
+  </si>
+  <si>
+    <t>9.41820035266836</t>
+  </si>
+  <si>
+    <t>23.08850256926759</t>
+  </si>
+  <si>
+    <t>9.55176089315875</t>
+  </si>
+  <si>
+    <t>0.3143805877181892</t>
+  </si>
+  <si>
+    <t>9.369468604320986</t>
+  </si>
+  <si>
+    <t>0.285608302202562</t>
+  </si>
+  <si>
+    <t>9.430261146874198</t>
+  </si>
+  <si>
+    <t>2.308926809924802</t>
+  </si>
+  <si>
+    <t>9.413978573113228</t>
+  </si>
+  <si>
+    <t>3.155742522492386</t>
+  </si>
+  <si>
+    <t>9.54248072241856</t>
+  </si>
+  <si>
+    <t>3.9937328020851397</t>
+  </si>
+  <si>
+    <t>9.90725407869685</t>
+  </si>
+  <si>
+    <t>3.8306913455811027</t>
+  </si>
+  <si>
+    <t>9.563377646610958</t>
+  </si>
+  <si>
+    <t>3.9141536264329093</t>
+  </si>
+  <si>
+    <t>9.95210146966662</t>
+  </si>
+  <si>
+    <t>4.829906541761011</t>
+  </si>
+  <si>
+    <t>9.343353891401977</t>
+  </si>
+  <si>
+    <t>6.4445471540818255</t>
+  </si>
+  <si>
+    <t>10.687423571552117</t>
+  </si>
+  <si>
+    <t>5.953289014662515</t>
+  </si>
+  <si>
+    <t>10.22593029508541</t>
+  </si>
+  <si>
+    <t>6.8588641371809125</t>
   </si>
 </sst>
 </file>
@@ -565,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -611,25 +599,25 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
       </c>
       <c r="F10">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
       </c>
       <c r="H10">
-        <v>420</v>
+        <v>351</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
@@ -638,10 +626,10 @@
         <v>16</v>
       </c>
       <c r="K10">
-        <v>0.1618945836207179</v>
+        <v>0.17465558475822793</v>
       </c>
       <c r="L10">
-        <v>-4.31686899883841</v>
+        <v>-4.325105807524966</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -649,25 +637,25 @@
         <v>12</v>
       </c>
       <c r="B11">
+        <v>138</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11">
+        <v>556</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11">
         <v>161</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11">
-        <v>1149</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11">
-        <v>208</v>
-      </c>
       <c r="G11" t="s">
         <v>14</v>
       </c>
       <c r="H11">
-        <v>549</v>
+        <v>420</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -676,10 +664,10 @@
         <v>18</v>
       </c>
       <c r="K11">
-        <v>0.46767052134251863</v>
+        <v>0.42224720882219396</v>
       </c>
       <c r="L11">
-        <v>-4.312634483181437</v>
+        <v>-4.274095936934364</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -687,25 +675,25 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
       </c>
       <c r="F12">
-        <v>254</v>
+        <v>208</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
       </c>
       <c r="H12">
-        <v>675</v>
+        <v>549</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
@@ -714,10 +702,10 @@
         <v>20</v>
       </c>
       <c r="K12">
-        <v>0.4228517294370611</v>
+        <v>0.6609005679087013</v>
       </c>
       <c r="L12">
-        <v>-4.324579059278603</v>
+        <v>1.7010585732606156</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -725,25 +713,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
       </c>
       <c r="F13">
-        <v>330</v>
+        <v>212</v>
       </c>
       <c r="G13" t="s">
         <v>14</v>
       </c>
       <c r="H13">
-        <v>891</v>
+        <v>561</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -752,10 +740,10 @@
         <v>22</v>
       </c>
       <c r="K13">
-        <v>0.7304056517271192</v>
+        <v>0.7039197239670706</v>
       </c>
       <c r="L13">
-        <v>-4.326543589560318</v>
+        <v>1.700607761981143</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -763,25 +751,25 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E14" t="s">
         <v>13</v>
       </c>
       <c r="F14">
-        <v>424</v>
+        <v>254</v>
       </c>
       <c r="G14" t="s">
         <v>14</v>
       </c>
       <c r="H14">
-        <v>1161</v>
+        <v>675</v>
       </c>
       <c r="I14" t="s">
         <v>23</v>
@@ -790,10 +778,10 @@
         <v>24</v>
       </c>
       <c r="K14">
-        <v>0.7995644409823222</v>
+        <v>0.7164602319964201</v>
       </c>
       <c r="L14">
-        <v>1.4445621770364154</v>
+        <v>1.3584324971575712</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -801,25 +789,25 @@
         <v>12</v>
       </c>
       <c r="B15">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
       </c>
       <c r="D15">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
       </c>
       <c r="F15">
-        <v>556</v>
+        <v>285</v>
       </c>
       <c r="G15" t="s">
         <v>14</v>
       </c>
       <c r="H15">
-        <v>1545</v>
+        <v>768</v>
       </c>
       <c r="I15" t="s">
         <v>25</v>
@@ -828,10 +816,10 @@
         <v>26</v>
       </c>
       <c r="K15">
-        <v>0.8683106041725921</v>
+        <v>0.8177766396505066</v>
       </c>
       <c r="L15">
-        <v>1.2804360465067373</v>
+        <v>1.4708514345310704</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -839,25 +827,25 @@
         <v>12</v>
       </c>
       <c r="B16">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
       <c r="D16">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E16" t="s">
         <v>13</v>
       </c>
       <c r="F16">
-        <v>657</v>
+        <v>330</v>
       </c>
       <c r="G16" t="s">
         <v>14</v>
       </c>
       <c r="H16">
-        <v>1836</v>
+        <v>891</v>
       </c>
       <c r="I16" t="s">
         <v>27</v>
@@ -866,10 +854,10 @@
         <v>28</v>
       </c>
       <c r="K16">
-        <v>0.9020399683801745</v>
+        <v>0.8467165692959375</v>
       </c>
       <c r="L16">
-        <v>0.834294765087806</v>
+        <v>1.4358636886441924</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -877,25 +865,25 @@
         <v>12</v>
       </c>
       <c r="B17">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
       </c>
       <c r="D17">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E17" t="s">
         <v>13</v>
       </c>
       <c r="F17">
-        <v>781</v>
+        <v>365</v>
       </c>
       <c r="G17" t="s">
         <v>14</v>
       </c>
       <c r="H17">
-        <v>2196</v>
+        <v>996</v>
       </c>
       <c r="I17" t="s">
         <v>29</v>
@@ -904,10 +892,10 @@
         <v>30</v>
       </c>
       <c r="K17">
-        <v>0.8942669442522718</v>
+        <v>0.7437061014104351</v>
       </c>
       <c r="L17">
-        <v>0.5187443987349244</v>
+        <v>1.2795488414188718</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -915,25 +903,25 @@
         <v>12</v>
       </c>
       <c r="B18">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
       </c>
       <c r="D18">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
       </c>
       <c r="F18">
-        <v>899</v>
+        <v>424</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
       </c>
       <c r="H18">
-        <v>2538</v>
+        <v>1161</v>
       </c>
       <c r="I18" t="s">
         <v>31</v>
@@ -942,10 +930,10 @@
         <v>32</v>
       </c>
       <c r="K18">
-        <v>0.919614912391808</v>
+        <v>0.9030263772980619</v>
       </c>
       <c r="L18">
-        <v>0.12262134684195229</v>
+        <v>0.9159901747569148</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -953,25 +941,25 @@
         <v>12</v>
       </c>
       <c r="B19">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
       </c>
       <c r="D19">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
       </c>
       <c r="F19">
-        <v>1008</v>
+        <v>462</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
       </c>
       <c r="H19">
-        <v>2853</v>
+        <v>1275</v>
       </c>
       <c r="I19" t="s">
         <v>33</v>
@@ -980,10 +968,10 @@
         <v>34</v>
       </c>
       <c r="K19">
-        <v>0.8862736955871354</v>
+        <v>0.9430346718535948</v>
       </c>
       <c r="L19">
-        <v>0.03500059493404558</v>
+        <v>0.8044247380882235</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -991,25 +979,25 @@
         <v>12</v>
       </c>
       <c r="B20">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
       </c>
       <c r="D20">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E20" t="s">
         <v>13</v>
       </c>
       <c r="F20">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="G20" t="s">
         <v>14</v>
       </c>
       <c r="H20">
-        <v>3264</v>
+        <v>1545</v>
       </c>
       <c r="I20" t="s">
         <v>35</v>
@@ -1018,10 +1006,10 @@
         <v>36</v>
       </c>
       <c r="K20">
-        <v>0.9038691840152521</v>
+        <v>0.9739679249188503</v>
       </c>
       <c r="L20">
-        <v>1.1469771432750429</v>
+        <v>1.3633957671747567</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1029,25 +1017,25 @@
         <v>12</v>
       </c>
       <c r="B21">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
       <c r="D21">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E21" t="s">
         <v>13</v>
       </c>
       <c r="F21">
-        <v>1295</v>
+        <v>649</v>
       </c>
       <c r="G21" t="s">
         <v>14</v>
       </c>
       <c r="H21">
-        <v>3690</v>
+        <v>1812</v>
       </c>
       <c r="I21" t="s">
         <v>37</v>
@@ -1056,10 +1044,10 @@
         <v>38</v>
       </c>
       <c r="K21">
-        <v>0.9162393134690018</v>
+        <v>0.9800834423362293</v>
       </c>
       <c r="L21">
-        <v>-2.2121119821639756</v>
+        <v>-0.502544278495075</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1067,25 +1055,25 @@
         <v>12</v>
       </c>
       <c r="B22">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
       <c r="D22">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E22" t="s">
         <v>13</v>
       </c>
       <c r="F22">
-        <v>1450</v>
+        <v>657</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
       </c>
       <c r="H22">
-        <v>4143</v>
+        <v>1836</v>
       </c>
       <c r="I22" t="s">
         <v>39</v>
@@ -1094,10 +1082,10 @@
         <v>40</v>
       </c>
       <c r="K22">
-        <v>0.9523000633205281</v>
+        <v>0.9717149602842069</v>
       </c>
       <c r="L22">
-        <v>-0.8718681972316293</v>
+        <v>-0.5442291724268327</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1105,25 +1093,25 @@
         <v>12</v>
       </c>
       <c r="B23">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="D23">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E23" t="s">
         <v>13</v>
       </c>
       <c r="F23">
-        <v>1625</v>
+        <v>781</v>
       </c>
       <c r="G23" t="s">
         <v>14</v>
       </c>
       <c r="H23">
-        <v>4656</v>
+        <v>2196</v>
       </c>
       <c r="I23" t="s">
         <v>41</v>
@@ -1132,10 +1120,10 @@
         <v>42</v>
       </c>
       <c r="K23">
-        <v>0.9277107537274091</v>
+        <v>0.9745237195746616</v>
       </c>
       <c r="L23">
-        <v>-0.7304323025814538</v>
+        <v>0.3634101665466384</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1143,25 +1131,25 @@
         <v>12</v>
       </c>
       <c r="B24">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
       </c>
       <c r="D24">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E24" t="s">
         <v>13</v>
       </c>
       <c r="F24">
-        <v>1827</v>
+        <v>806</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
       </c>
       <c r="H24">
-        <v>5250</v>
+        <v>2271</v>
       </c>
       <c r="I24" t="s">
         <v>43</v>
@@ -1170,10 +1158,10 @@
         <v>44</v>
       </c>
       <c r="K24">
-        <v>0.9394346877367572</v>
+        <v>0.9737732054864844</v>
       </c>
       <c r="L24">
-        <v>-0.7280573951712116</v>
+        <v>0.49910156183066673</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1181,25 +1169,25 @@
         <v>12</v>
       </c>
       <c r="B25">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
       </c>
       <c r="D25">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E25" t="s">
         <v>13</v>
       </c>
       <c r="F25">
-        <v>2033</v>
+        <v>899</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
       </c>
       <c r="H25">
-        <v>5856</v>
+        <v>2538</v>
       </c>
       <c r="I25" t="s">
         <v>45</v>
@@ -1208,10 +1196,10 @@
         <v>46</v>
       </c>
       <c r="K25">
-        <v>0.9594137993863016</v>
+        <v>0.9796612912665961</v>
       </c>
       <c r="L25">
-        <v>-0.5319556095582736</v>
+        <v>0.6013790053364395</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1219,25 +1207,25 @@
         <v>12</v>
       </c>
       <c r="B26">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
       </c>
       <c r="D26">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E26" t="s">
         <v>13</v>
       </c>
       <c r="F26">
-        <v>2279</v>
+        <v>940</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
       </c>
       <c r="H26">
-        <v>6582</v>
+        <v>2661</v>
       </c>
       <c r="I26" t="s">
         <v>47</v>
@@ -1246,10 +1234,10 @@
         <v>48</v>
       </c>
       <c r="K26">
-        <v>0.9276235227850402</v>
+        <v>0.9959533009314888</v>
       </c>
       <c r="L26">
-        <v>-0.5377668961976602</v>
+        <v>0.5832771605157976</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1257,25 +1245,25 @@
         <v>12</v>
       </c>
       <c r="B27">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
       </c>
       <c r="D27">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E27" t="s">
         <v>13</v>
       </c>
       <c r="F27">
-        <v>2498</v>
+        <v>1008</v>
       </c>
       <c r="G27" t="s">
         <v>14</v>
       </c>
       <c r="H27">
-        <v>7227</v>
+        <v>2853</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1284,10 +1272,10 @@
         <v>50</v>
       </c>
       <c r="K27">
-        <v>0.9590595011138769</v>
+        <v>0.9806113058965723</v>
       </c>
       <c r="L27">
-        <v>-0.49450413640320956</v>
+        <v>0.5926378672603426</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1295,25 +1283,25 @@
         <v>12</v>
       </c>
       <c r="B28">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
       </c>
       <c r="D28">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E28" t="s">
         <v>13</v>
       </c>
       <c r="F28">
-        <v>2737</v>
+        <v>1062</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
       </c>
       <c r="H28">
-        <v>7932</v>
+        <v>3015</v>
       </c>
       <c r="I28" t="s">
         <v>51</v>
@@ -1322,10 +1310,10 @@
         <v>52</v>
       </c>
       <c r="K28">
-        <v>0.9429029844671526</v>
+        <v>0.9979147953503247</v>
       </c>
       <c r="L28">
-        <v>-0.4805403749334304</v>
+        <v>0.6839387272752866</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1333,25 +1321,25 @@
         <v>12</v>
       </c>
       <c r="B29">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
       </c>
       <c r="D29">
+        <v>556</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29">
         <v>1149</v>
       </c>
-      <c r="E29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29">
-        <v>2918</v>
-      </c>
       <c r="G29" t="s">
         <v>14</v>
       </c>
       <c r="H29">
-        <v>8463</v>
+        <v>3264</v>
       </c>
       <c r="I29" t="s">
         <v>53</v>
@@ -1360,10 +1348,10 @@
         <v>54</v>
       </c>
       <c r="K29">
-        <v>0.9484091187499624</v>
+        <v>0.9705027986145746</v>
       </c>
       <c r="L29">
-        <v>-0.46938396037013536</v>
+        <v>0.8091924057246411</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1371,25 +1359,25 @@
         <v>12</v>
       </c>
       <c r="B30">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
       </c>
       <c r="D30">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E30" t="s">
         <v>13</v>
       </c>
       <c r="F30">
-        <v>3203</v>
+        <v>1194</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
       </c>
       <c r="H30">
-        <v>9306</v>
+        <v>3399</v>
       </c>
       <c r="I30" t="s">
         <v>55</v>
@@ -1398,10 +1386,10 @@
         <v>56</v>
       </c>
       <c r="K30">
-        <v>0.9377524005988025</v>
+        <v>1.0288730219985112</v>
       </c>
       <c r="L30">
-        <v>-0.4237450181914542</v>
+        <v>0.7747569667826147</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1409,25 +1397,25 @@
         <v>12</v>
       </c>
       <c r="B31">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
       </c>
       <c r="D31">
-        <v>1149</v>
+        <v>556</v>
       </c>
       <c r="E31" t="s">
         <v>13</v>
       </c>
       <c r="F31">
-        <v>3411</v>
+        <v>1295</v>
       </c>
       <c r="G31" t="s">
         <v>14</v>
       </c>
       <c r="H31">
-        <v>9918</v>
+        <v>3690</v>
       </c>
       <c r="I31" t="s">
         <v>57</v>
@@ -1436,86 +1424,10 @@
         <v>58</v>
       </c>
       <c r="K31">
-        <v>0.9364994852050696</v>
+        <v>1.0097028280381866</v>
       </c>
       <c r="L31">
-        <v>-0.5525661533544703</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32">
-        <v>161</v>
-      </c>
-      <c r="C32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32">
-        <v>1149</v>
-      </c>
-      <c r="E32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32">
-        <v>3691</v>
-      </c>
-      <c r="G32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32">
-        <v>10746</v>
-      </c>
-      <c r="I32" t="s">
-        <v>59</v>
-      </c>
-      <c r="J32" t="s">
-        <v>60</v>
-      </c>
-      <c r="K32">
-        <v>0.954057490731138</v>
-      </c>
-      <c r="L32">
-        <v>-0.6404243840933851</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33">
-        <v>161</v>
-      </c>
-      <c r="C33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33">
-        <v>1149</v>
-      </c>
-      <c r="E33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33">
-        <v>3936</v>
-      </c>
-      <c r="G33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33">
-        <v>11469</v>
-      </c>
-      <c r="I33" t="s">
-        <v>61</v>
-      </c>
-      <c r="J33" t="s">
-        <v>62</v>
-      </c>
-      <c r="K33">
-        <v>0.9406287409850647</v>
-      </c>
-      <c r="L33">
-        <v>-0.6286495994506933</v>
+        <v>0.8362522002842031</v>
       </c>
     </row>
   </sheetData>
